--- a/verification/cases/roundtrip/theme_linked_colors/init.xlsx
+++ b/verification/cases/roundtrip/theme_linked_colors/init.xlsx
@@ -1,15 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-1516826600\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5098235C-A738-49E0-9B41-076B90B5A773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>theme-linked</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -19,7 +39,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="4" tint="0.2"/>
+      <color theme="4" tint="0.19998779259620961"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -49,6 +69,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -158,19 +191,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>theme-linked</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>